--- a/backtest_runs/20260410_193731/by_symbol/BRRG/BRRG.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/BRRG/BRRG.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1662.080000000002</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99870.14999999999</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>99870.14999999999</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100882.98</v>
@@ -863,7 +863,7 @@
         <v>-415.5200000000096</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>100467.46</v>
@@ -909,7 +909,7 @@
         <v>-519.4000000000074</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>99948.05999999997</v>
@@ -955,7 +955,7 @@
         <v>-1038.799999999996</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>98909.25999999998</v>
@@ -1139,7 +1139,7 @@
         <v>-2415.209999999999</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>100545.37</v>
@@ -1231,7 +1231,7 @@
         <v>-2337.299999999996</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>98208.06999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-1921.780000000005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>96286.28999999998</v>
@@ -1553,7 +1553,7 @@
         <v>-4129.230000000009</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>95818.82999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-1506.259999999996</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>94312.56999999999</v>
